--- a/business/alaga/ALAGA-FLEX-model.xlsx
+++ b/business/alaga/ALAGA-FLEX-model.xlsx
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -215,6 +215,7 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -305,6 +306,11 @@
     <comment ref="C26" authorId="0" shapeId="0">
       <text>
         <t>Model is more sensitive to this than to FOB cost. Track cohort reorder rate weekly from launch. Operating manual kill criterion: abandon if under 15% by month 4.</t>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0" shapeId="0">
+      <text>
+        <t>CORRECTED 2 Sep 2026. Previously 0.78/month, which implied only ~5% of the repeat base surviving 12 months — far below observed behaviour. Benchmarks: pet subscription monthly plans churn 18-22% per year, quarterly 11-16%, and subscription pet brands retain 60%+ of customers past month 12. 0.990/month compounds to ~89% annual retention (quarterly billing); 0.982 gives ~80% (monthly billing).</t>
       </text>
     </comment>
   </commentList>
@@ -600,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B39"/>
+  <dimension ref="B2:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -755,7 +761,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>WHAT THE MODEL SAYS AT THESE PLACEHOLDER NUMBERS</t>
         </is>
@@ -764,28 +770,28 @@
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Landed cost decides payback, not repeat rate. Tested across both supplier lanes:</t>
+          <t>China lane (FOB $4.00, MOQ 1,000): capital ~PHP 920,000 · payback month 13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · China lane (FOB $4.00, MOQ 1,000): capital ≈ PHP 918,000 · payback ≈ month 15</t>
+          <t>US lane (FOB $7.00, MOQ 2,500): capital ~PHP 2,091,000 · payback month 21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · US lane (FOB $7.00, MOQ 2,500): capital ≈ PHP 2,082,000 · payback beyond 24 months</t>
+          <t>Both now clear the 24-30 month screen. The China lane still wins on cash,</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Varying repeat conversion from 10% to 45% moves China payback only 17 → 15 months.</t>
+          <t>but the US lane is viable, which it was not before the retention correction below.</t>
         </is>
       </c>
     </row>
@@ -799,28 +805,35 @@
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>dominate. Repeat rate still governs long-run value and every year after year two —</t>
+          <t>RETENTION CORRECTION — 2 Sep 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>track it — but do not let it decide the supplier. The supplier quote decides payback.</t>
+          <t>This model originally assumed 0.78 monthly retention, implying ~5% of repeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>customers survive a year. Published pet-subscription benchmarks put retention at</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>CONSEQUENCE: the US lane only works if a real quote beats these placeholders —</t>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>60%+ past month 12. Corrected to 0.990 (quarterly billing). Effect: 24-month</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>roughly FOB at or below $5.00, or MOQ at or below 1,500. Ask for both in the RFQ.</t>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>EBITDA roughly doubles, PHP 3.6M to PHP 6.7M, and payback moves 15 to 13 months.</t>
         </is>
       </c>
     </row>
@@ -828,6 +841,49 @@
       <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Note too that US-lane wholesale margin lands at ~29%, just under the 30% screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="46" t="inlineStr">
+        <is>
+          <t>CONSEQUENCE FOR REPEAT RATE: with retention corrected, repeat customers are ~72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="46" t="inlineStr">
+        <is>
+          <t>of month-24 volume. Repeat conversion from 10% to 45% swings 24-month EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="46" t="inlineStr">
+        <is>
+          <t>2.4x (PHP 3.3M to 8.1M) while moving payback only 16 to 13 months. So repeat rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>sets what the business earns and is worth; landed cost sets when it pays back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Sell QUARTERLY by default. Benchmarks: monthly plans churn 18-22%/yr, quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>11-16%/yr, and longer billing cadence cuts churn without raising acquisition cost.</t>
         </is>
       </c>
     </row>
@@ -1138,11 +1194,11 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Quarterly billing. Use 0.982 if billing monthly.</t>
         </is>
       </c>
     </row>
@@ -1173,6 +1229,13 @@
       <c r="D29" s="10" t="inlineStr">
         <is>
           <t>1.0 = base. Scenarios tab uses 0.6 / 1.0 / 1.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Billing cadence note: quarterly billing cuts churn without raising CAC.</t>
         </is>
       </c>
     </row>
